--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -848,11 +848,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfallet, Mpd</t>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28584-2026 artfynd.xlsx
+++ b/artfynd/A 28584-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>130669627</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
